--- a/EXAMPLE.xlsx
+++ b/EXAMPLE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489E1410-130A-4864-80FE-2B898FAC24A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDB7D9B-0B62-4244-B690-71D36C1EFDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3DC27B79-1929-414A-AB84-D9FF00956244}"/>
+    <workbookView xWindow="20" yWindow="380" windowWidth="19180" windowHeight="9810" xr2:uid="{3DC27B79-1929-414A-AB84-D9FF00956244}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="141">
   <si>
     <t>Language</t>
   </si>
@@ -162,9 +162,6 @@
     <t>Western Armenian</t>
   </si>
   <si>
-    <t>Batua</t>
-  </si>
-  <si>
     <t>Karin</t>
   </si>
   <si>
@@ -547,6 +544,15 @@
   </si>
   <si>
     <t>Tungusic</t>
+  </si>
+  <si>
+    <t>Gipuzkera</t>
+  </si>
+  <si>
+    <t>41° 23' 11.6196'' N</t>
+  </si>
+  <si>
+    <t>2° 9' 47.9916'' E</t>
   </si>
 </sst>
 </file>
@@ -650,10 +656,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -997,66 +999,66 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -1064,58 +1066,64 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
+      <c r="D6">
+        <v>43.313718999999999</v>
+      </c>
+      <c r="E6">
+        <v>-1.9828170000000001</v>
+      </c>
       <c r="F6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -1126,307 +1134,313 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="D10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" t="s">
+        <v>140</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" t="s">
         <v>134</v>
       </c>
-      <c r="C22" t="s">
-        <v>135</v>
-      </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -1434,470 +1448,470 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F44" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" t="s">
         <v>64</v>
       </c>
-      <c r="B45" t="s">
-        <v>65</v>
-      </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C49" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" t="s">
         <v>137</v>
       </c>
-      <c r="C52" t="s">
-        <v>138</v>
-      </c>
       <c r="F52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F53" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G53" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F54" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C55" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G56" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C57" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G57" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G59" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C60" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C61" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C63" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G63" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
@@ -1905,58 +1919,64 @@
         <v>9</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="D65">
+        <v>40.603603999999997</v>
+      </c>
+      <c r="E65">
+        <v>43.098156000000003</v>
       </c>
       <c r="F65" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C66" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C67" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F67" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F68" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G68" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
